--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E8" s="3">
         <v>85500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>69700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>44700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>40800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>23400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17400</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5800</v>
-      </c>
-      <c r="W9" s="3">
-        <v>5400</v>
       </c>
       <c r="X9" s="3">
         <v>5400</v>
       </c>
       <c r="Y9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Z9" s="3">
         <v>5200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E10" s="3">
         <v>65300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>61100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>43400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>40000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22300</v>
-      </c>
-      <c r="S10" s="3">
-        <v>19200</v>
       </c>
       <c r="T10" s="3">
         <v>19200</v>
       </c>
       <c r="U10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="V10" s="3">
         <v>18600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12400</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,61 +1042,62 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E12" s="3">
         <v>20100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7800</v>
-      </c>
-      <c r="P12" s="3">
-        <v>7700</v>
       </c>
       <c r="Q12" s="3">
         <v>7700</v>
       </c>
       <c r="R12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="S12" s="3">
         <v>7300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8900</v>
-      </c>
-      <c r="T12" s="3">
-        <v>6400</v>
       </c>
       <c r="U12" s="3">
         <v>6400</v>
@@ -1096,19 +1109,22 @@
         <v>6400</v>
       </c>
       <c r="X12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="Y12" s="3">
         <v>6300</v>
       </c>
       <c r="Z12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>6500</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E17" s="3">
         <v>109700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>94200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>87100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>82800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>79700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>76000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>67000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>41500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>35600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,38 +1579,39 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1586,19 +1619,19 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
@@ -1613,7 +1646,7 @@
         <v>200</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
@@ -1621,97 +1654,103 @@
       <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-24400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-2700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
@@ -1725,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1764,107 +1803,113 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
@@ -1891,16 +1936,16 @@
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1929,11 +1974,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,38 +2537,41 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2510,19 +2579,19 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
@@ -2537,7 +2606,7 @@
         <v>-200</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
@@ -2545,88 +2614,94 @@
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E41" s="3">
         <v>41100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>79900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>95100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>81700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>115300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>108300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>102300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>117800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>79800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>137400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,56 +3082,59 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E42" s="3">
         <v>71900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>106100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>105200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>69800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>63200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>65500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>49400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>49500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>49700</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3150,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3073,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E43" s="3">
         <v>45100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>42300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>36700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>35800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3227,68 +3322,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E45" s="3">
         <v>38100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,68 +3402,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>195900</v>
+      </c>
+      <c r="E46" s="3">
         <v>196200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>259300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>235500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>225200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>223800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>226800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>222500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>210100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>205100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>200900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>199300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>193700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>154400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>161100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>157000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>30800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>35700</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,35 +3482,38 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E47" s="3">
         <v>8400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3425,8 +3529,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3458,68 +3562,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E48" s="3">
         <v>20000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,68 +3642,71 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E49" s="3">
         <v>152300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,68 +3882,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E52" s="3">
         <v>23300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5900</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E54" s="3">
         <v>400300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>324500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>309600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>293900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>278500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>275300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>270500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>264700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>250600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>245600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>241200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>239700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>232300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>191800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>198500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>189600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4132,8 +4262,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4209,68 +4342,71 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>174100</v>
+      </c>
+      <c r="E59" s="3">
         <v>151800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>148400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>140600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>127800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>112300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>107300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>102600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>76600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>72400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>47500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>41000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>37600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,68 +4422,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E60" s="3">
         <v>163300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>157700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>146300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>132800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>114000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>98400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>73000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>67600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>63600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>47000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,17 +4502,20 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E61" s="3">
         <v>75000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -4440,68 +4582,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E62" s="3">
         <v>17100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>24000</v>
       </c>
       <c r="P62" s="3">
         <v>24000</v>
       </c>
       <c r="Q62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="R62" s="3">
         <v>23100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>252400</v>
+      </c>
+      <c r="E66" s="3">
         <v>255400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>175300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>164900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>151600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>138800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>134300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>127700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>119500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>102700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>87600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>61500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5062,13 +5229,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>103000</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-292400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-272300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-249300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-236200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-226000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-214000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-200100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-185500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-175700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-165800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-158900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-153400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-147000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-141200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-134200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-125900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-115400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-84500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E76" s="3">
         <v>144900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>149100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>144800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>142300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>139700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>141100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>142800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>145200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>148000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>150200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>150400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>152100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>119000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>128000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>128100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-95100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-90200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,22 +6009,23 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
@@ -5857,29 +6055,29 @@
         <v>1000</v>
       </c>
       <c r="Q83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
       </c>
       <c r="S83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>1300</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>1000</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,74 +6487,77 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>4400</v>
       </c>
       <c r="M89" s="3">
         <v>4400</v>
       </c>
       <c r="N89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>-4900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6351,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,74 +6599,75 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-400</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-200</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>-200</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,74 +6837,77 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-8700</v>
       </c>
       <c r="F94" s="3">
         <v>-8700</v>
       </c>
       <c r="G94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-18900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-200</v>
       </c>
       <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>-200</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,74 +7267,77 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E100" s="3">
         <v>73700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>42000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>127600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>29700</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7102,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,74 +7427,77 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-57600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>122700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>24600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7254,6 +7505,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E8" s="3">
         <v>93600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>85500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>69700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>65300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>61400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>53300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>44700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>40800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17400</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E9" s="3">
         <v>21000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5800</v>
-      </c>
-      <c r="X9" s="3">
-        <v>5400</v>
       </c>
       <c r="Y9" s="3">
         <v>5400</v>
       </c>
       <c r="Z9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AA9" s="3">
         <v>5200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5000</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E10" s="3">
         <v>72600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>61100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>58300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>43400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>30800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22300</v>
-      </c>
-      <c r="T10" s="3">
-        <v>19200</v>
       </c>
       <c r="U10" s="3">
         <v>19200</v>
       </c>
       <c r="V10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="W10" s="3">
         <v>18600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>15000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12400</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,64 +1056,65 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E12" s="3">
         <v>22700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7700</v>
       </c>
       <c r="R12" s="3">
         <v>7700</v>
       </c>
       <c r="S12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="T12" s="3">
         <v>7300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>6400</v>
       </c>
       <c r="V12" s="3">
         <v>6400</v>
@@ -1112,19 +1126,22 @@
         <v>6400</v>
       </c>
       <c r="Y12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="Z12" s="3">
         <v>6300</v>
       </c>
       <c r="AA12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>6500</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E17" s="3">
         <v>111800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>94200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>87100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>82800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>79700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>76000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>67000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>41500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>31500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>23900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-26000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,41 +1613,42 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1622,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
@@ -1649,7 +1683,7 @@
         <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
@@ -1657,103 +1691,109 @@
       <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-24400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
@@ -1767,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1806,113 +1846,119 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
       </c>
       <c r="Z22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-25800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -1939,16 +1985,16 @@
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1977,11 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-25900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-25900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,41 +2607,44 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2582,19 +2652,19 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
@@ -2609,7 +2679,7 @@
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
@@ -2617,91 +2687,97 @@
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-25900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-25900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,71 +3091,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E41" s="3">
         <v>49800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>79900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>68600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>107100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>115300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>102300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>114500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>117800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>79800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>137400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18800</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,59 +3172,62 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E42" s="3">
         <v>44600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>71900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>106100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>77000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>105200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>97700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>69800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>63200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>65500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>49400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>49500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>49700</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,8 +3243,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3165,71 +3255,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E43" s="3">
         <v>63500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>36700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>35800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3325,71 +3421,74 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E45" s="3">
         <v>38000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,71 +3504,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E46" s="3">
         <v>195900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>196200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>259300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>246400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>235500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>225200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>223800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>226800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>222500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>210100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>205100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>199300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>193700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>154400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>161100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>157000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>35700</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,38 +3587,41 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3637,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3565,71 +3670,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E48" s="3">
         <v>20100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,71 +3753,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E49" s="3">
         <v>149500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>152300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,71 +4002,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E52" s="3">
         <v>27300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5900</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,71 +4168,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>389900</v>
+      </c>
+      <c r="E54" s="3">
         <v>396600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>400300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>324500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>309600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>293900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>278500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>275300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>270500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>264700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>250600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>245600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>241200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>239700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>232300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>191800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>198500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>189600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,71 +4315,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4345,71 +4479,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>176700</v>
+      </c>
+      <c r="E59" s="3">
         <v>174100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>151800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>148400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>140600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>127800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>112300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>107300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>102600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>76600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>66900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>62000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>47500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>41000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>37600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,71 +4562,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E60" s="3">
         <v>181000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>163300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>157700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>146300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>132800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>119500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>114000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>107300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>98400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>73000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>67600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>63600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>49700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,20 +4645,23 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E61" s="3">
         <v>55000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>75000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -4585,71 +4728,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E62" s="3">
         <v>16400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>24000</v>
       </c>
       <c r="Q62" s="3">
         <v>24000</v>
       </c>
       <c r="R62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="S62" s="3">
         <v>23100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>19500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,71 +5060,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E66" s="3">
         <v>252400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>255400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>175300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>164900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>151600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>138800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>134300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>127700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>119500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>102700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>95500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>87600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>72800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>61500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5232,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>103000</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5506,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-292400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-249300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-236200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-226000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-214000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-200100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-185500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-175700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-165800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-158900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-153400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-147000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-141200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-134200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-125900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-115400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-84500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,71 +5838,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E76" s="3">
         <v>144200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>144900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>149100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>144800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>142300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>139700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>141100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>142800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>145200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>148000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>150200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>150400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>152100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>119000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>128000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>128100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-95100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-90200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-25900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,25 +6208,26 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
@@ -6058,29 +6257,29 @@
         <v>1000</v>
       </c>
       <c r="R83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
       </c>
       <c r="T83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>1300</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,77 +6704,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>4400</v>
       </c>
       <c r="N89" s="3">
         <v>4400</v>
       </c>
       <c r="O89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,77 +6820,78 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-400</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
       </c>
       <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-200</v>
       </c>
       <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>-200</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,77 +7067,80 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E94" s="3">
         <v>32200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-8700</v>
       </c>
       <c r="G94" s="3">
         <v>-8700</v>
       </c>
       <c r="H94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-18900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>25900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-200</v>
       </c>
       <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>-200</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,77 +7513,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>73700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>42000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>127600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3">
         <v>29700</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,77 +7679,80 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E102" s="3">
         <v>9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-33300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-57600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>122700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3">
         <v>24600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -656,212 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E8" s="3">
         <v>96800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>93600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>85500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>79300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>69700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>65300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>53300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>40800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>23400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17400</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -869,165 +876,171 @@
         <v>22400</v>
       </c>
       <c r="E9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F9" s="3">
         <v>21000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5800</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>5400</v>
       </c>
       <c r="Z9" s="3">
         <v>5400</v>
       </c>
       <c r="AA9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AB9" s="3">
         <v>5200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E10" s="3">
         <v>74400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>65300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>58300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>54300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>50000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>46300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>40000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>30800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22300</v>
-      </c>
-      <c r="U10" s="3">
-        <v>19200</v>
       </c>
       <c r="V10" s="3">
         <v>19200</v>
       </c>
       <c r="W10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="X10" s="3">
         <v>18600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>15000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12400</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,67 +1070,68 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E12" s="3">
         <v>23800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
-      </c>
-      <c r="R12" s="3">
-        <v>7700</v>
       </c>
       <c r="S12" s="3">
         <v>7700</v>
       </c>
       <c r="T12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="U12" s="3">
         <v>7300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8900</v>
-      </c>
-      <c r="V12" s="3">
-        <v>6400</v>
       </c>
       <c r="W12" s="3">
         <v>6400</v>
@@ -1129,19 +1143,22 @@
         <v>6400</v>
       </c>
       <c r="Z12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AA12" s="3">
         <v>6300</v>
       </c>
       <c r="AB12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AC12" s="3">
         <v>6500</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>115900</v>
+      </c>
+      <c r="E17" s="3">
         <v>110100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>111800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>109700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>94200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>87100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>82800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>79700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>76000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>54100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>35600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-26000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,44 +1647,45 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1659,19 +1693,19 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
@@ -1686,7 +1720,7 @@
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -1694,94 +1728,100 @@
       <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-24400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1789,14 +1829,14 @@
         <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1810,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1849,119 +1889,125 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
       </c>
       <c r="AA22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-25800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
@@ -1988,16 +2034,16 @@
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2026,11 +2072,14 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-25900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-25900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,44 +2677,47 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2655,19 +2725,19 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
@@ -2682,7 +2752,7 @@
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -2690,94 +2760,100 @@
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-25900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-25900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,74 +3178,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E41" s="3">
         <v>69200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>79900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>95100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>81700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>107100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>115300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>108300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>102300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>114500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>117800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>79800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>137400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>135300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18800</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,62 +3262,65 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E42" s="3">
         <v>25000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>44600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>71900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>106100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>77000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>105200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>97700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>69800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>59700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>63200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>65500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>49400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>49500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>49700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3246,8 +3336,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E43" s="3">
         <v>50400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>42300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>35800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,74 +3520,77 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E45" s="3">
         <v>33100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,74 +3606,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E46" s="3">
         <v>177700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>195900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>196200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>259300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>246400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>235500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>225200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>223800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>226800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>222500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>210100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>205100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>199300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>193700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>154400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>161100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>157000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>35700</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,41 +3692,44 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>1000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3640,8 +3745,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3673,74 +3778,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E48" s="3">
         <v>19900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20600</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,74 +3864,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>146300</v>
+      </c>
+      <c r="E49" s="3">
         <v>147800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>149500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>152300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8500</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,74 +4122,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E52" s="3">
         <v>43500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,74 +4294,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>393600</v>
+      </c>
+      <c r="E54" s="3">
         <v>389900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>396600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>400300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>324500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>309600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>293900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>278500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>275300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>270500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>264700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>250600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>245600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>241200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>239700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>232300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>191800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>198500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>189600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,74 +4446,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4482,74 +4616,77 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E59" s="3">
         <v>176700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>151800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>148400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>140600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>127800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>112300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>107300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>95500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>76600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>66900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>62000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>47500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>41000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>37600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,74 +4702,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E60" s="3">
         <v>182400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>181000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>163300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>157700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>146300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>132800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>119500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>114000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>107300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>98400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>80900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>73000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>67600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>63600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>49700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,23 +4788,26 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E61" s="3">
         <v>45000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>75000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -4731,74 +4874,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E62" s="3">
         <v>15200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>24000</v>
       </c>
       <c r="R62" s="3">
         <v>24000</v>
       </c>
       <c r="S62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="T62" s="3">
         <v>23100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>19500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,74 +5218,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E66" s="3">
         <v>242600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>252400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>255400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>175300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>164900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>151600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>138800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>134300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>127700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>119500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>102700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>87600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>72800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>61500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>58300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5403,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>103000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,74 +5680,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-322900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-306000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-292400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-272300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-249300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-236200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-226000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-214000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-200100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-185500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-175700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-165800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-158900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-153400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-147000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-141200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-134200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-125900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-115400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-84500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,74 +6024,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E76" s="3">
         <v>147400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>144200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>144900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>149100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>144800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>142300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>139700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>141100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>142800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>145200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>148000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>150200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>150400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>152100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>156600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>119000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>128000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>128100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-95100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-90200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-25900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6218,19 +6417,19 @@
         <v>2500</v>
       </c>
       <c r="E83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
@@ -6260,29 +6459,29 @@
         <v>1000</v>
       </c>
       <c r="S83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
       </c>
       <c r="U83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>1300</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1000</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,80 +6921,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>11200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>4400</v>
       </c>
       <c r="O89" s="3">
         <v>4400</v>
       </c>
       <c r="P89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q89" s="3">
         <v>3600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,80 +7041,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
       </c>
       <c r="J91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-200</v>
       </c>
       <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>-200</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,80 +7297,83 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E94" s="3">
         <v>20100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-8700</v>
       </c>
       <c r="H94" s="3">
         <v>-8700</v>
       </c>
       <c r="I94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-18900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-200</v>
       </c>
       <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>-200</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,80 +7759,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>73700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>42000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>127600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3">
         <v>29700</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,80 +7931,83 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E102" s="3">
         <v>19700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-57600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>122700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3">
         <v>24600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E8" s="3">
         <v>99400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>96800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>93600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>85500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>79300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>69700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>57400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>53300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>44700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>23400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17400</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>22400</v>
+        <v>23200</v>
       </c>
       <c r="E9" s="3">
         <v>22400</v>
       </c>
       <c r="F9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="G9" s="3">
         <v>21000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5800</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>5400</v>
       </c>
       <c r="AA9" s="3">
         <v>5400</v>
       </c>
       <c r="AB9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AC9" s="3">
         <v>5200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5000</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E10" s="3">
         <v>77000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>72600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>61100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>58300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>30800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>27700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22300</v>
-      </c>
-      <c r="V10" s="3">
-        <v>19200</v>
       </c>
       <c r="W10" s="3">
         <v>19200</v>
       </c>
       <c r="X10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>18600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>15000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12400</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,70 +1084,71 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E12" s="3">
         <v>25100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
-      </c>
-      <c r="S12" s="3">
-        <v>7700</v>
       </c>
       <c r="T12" s="3">
         <v>7700</v>
       </c>
       <c r="U12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="V12" s="3">
         <v>7300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8900</v>
-      </c>
-      <c r="W12" s="3">
-        <v>6400</v>
       </c>
       <c r="X12" s="3">
         <v>6400</v>
@@ -1146,19 +1160,22 @@
         <v>6400</v>
       </c>
       <c r="AA12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AB12" s="3">
         <v>6300</v>
       </c>
       <c r="AC12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>6500</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,31 +1260,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>3800</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1329,31 +1349,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E17" s="3">
         <v>115900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>110100</v>
       </c>
-      <c r="F17" s="3">
-        <v>111800</v>
-      </c>
       <c r="G17" s="3">
-        <v>109700</v>
+        <v>107500</v>
       </c>
       <c r="H17" s="3">
+        <v>106000</v>
+      </c>
+      <c r="I17" s="3">
         <v>94200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>87100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>82800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>39700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>41500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>54100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>35600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-18200</v>
-      </c>
       <c r="G18" s="3">
-        <v>-24200</v>
+        <v>-14000</v>
       </c>
       <c r="H18" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-26000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,67 +1681,68 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>200</v>
+      </c>
+      <c r="V20" s="3">
         <v>600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
@@ -1723,7 +1757,7 @@
         <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
@@ -1731,115 +1765,121 @@
       <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-13200</v>
+        <v>-14500</v>
       </c>
       <c r="E21" s="3">
-        <v>-10200</v>
+        <v>-14200</v>
       </c>
       <c r="F21" s="3">
-        <v>-14700</v>
+        <v>-11200</v>
       </c>
       <c r="G21" s="3">
-        <v>-20900</v>
+        <v>-11600</v>
       </c>
       <c r="H21" s="3">
-        <v>-11700</v>
+        <v>-18800</v>
       </c>
       <c r="I21" s="3">
-        <v>-9000</v>
+        <v>-13900</v>
       </c>
       <c r="J21" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-24400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E22" s="3">
         <v>1000</v>
       </c>
       <c r="F22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
@@ -1853,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1892,125 +1932,131 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>200</v>
       </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -2037,16 +2083,16 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2075,11 +2121,14 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-25900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-25900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,67 +2747,70 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-800</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
@@ -2755,7 +2825,7 @@
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
@@ -2763,97 +2833,103 @@
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-25900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-25900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3265,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E41" s="3">
         <v>80900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>81700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>107100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>115300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>108300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>102300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>114500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>117800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>137400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>135300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>18800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,65 +3352,68 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>12300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>44600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>71900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>106100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>105200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>97700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>69800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>59700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>63200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>65500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>49400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>49500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>49700</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3339,8 +3429,8 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3351,77 +3441,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E43" s="3">
         <v>58600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9200</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,31 +3530,34 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3523,77 +3619,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>31300</v>
+        <v>17700</v>
       </c>
       <c r="E45" s="3">
-        <v>33100</v>
+        <v>16200</v>
       </c>
       <c r="F45" s="3">
-        <v>38000</v>
+        <v>14800</v>
       </c>
       <c r="G45" s="3">
-        <v>38100</v>
+        <v>27700</v>
       </c>
       <c r="H45" s="3">
-        <v>36600</v>
+        <v>24700</v>
       </c>
       <c r="I45" s="3">
-        <v>32300</v>
+        <v>23200</v>
       </c>
       <c r="J45" s="3">
+        <v>21700</v>
+      </c>
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>18300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,77 +3708,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E46" s="3">
         <v>183100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>177700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>195900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>196200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>259300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>235500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>225200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>223800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>226800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>222500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>210100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>205100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>199300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>193700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>154400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>161100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>157000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>30800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>35700</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,44 +3797,47 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>1000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3748,8 +3853,8 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3781,77 +3886,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E48" s="3">
         <v>19100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,77 +3975,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E49" s="3">
         <v>146300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>147800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>149500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>152300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,77 +4242,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>45200</v>
+        <v>1100</v>
       </c>
       <c r="E52" s="3">
-        <v>43500</v>
+        <v>1000</v>
       </c>
       <c r="F52" s="3">
-        <v>27300</v>
+        <v>1000</v>
       </c>
       <c r="G52" s="3">
-        <v>23300</v>
+        <v>1100</v>
       </c>
       <c r="H52" s="3">
-        <v>21200</v>
+        <v>1100</v>
       </c>
       <c r="I52" s="3">
-        <v>20300</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>19700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5900</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4420,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>388800</v>
+      </c>
+      <c r="E54" s="3">
         <v>393600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>389900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>396600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>400300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>324500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>309600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>293900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>278500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>275300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>270500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>264700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>250600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>245600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>241200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>239700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>232300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>191800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>198500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>189600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4577,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="3">
         <v>9800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,31 +4664,34 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4619,77 +4753,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>177300</v>
+        <v>149200</v>
       </c>
       <c r="E59" s="3">
-        <v>176700</v>
+        <v>148300</v>
       </c>
       <c r="F59" s="3">
-        <v>174100</v>
+        <v>146400</v>
       </c>
       <c r="G59" s="3">
-        <v>151800</v>
+        <v>140500</v>
       </c>
       <c r="H59" s="3">
-        <v>148400</v>
+        <v>122500</v>
       </c>
       <c r="I59" s="3">
-        <v>140600</v>
+        <v>115900</v>
       </c>
       <c r="J59" s="3">
+        <v>109100</v>
+      </c>
+      <c r="K59" s="3">
         <v>127800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>112300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>107300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>76600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>66900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>62000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>47500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>41000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>36400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,77 +4842,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E60" s="3">
         <v>187100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>182400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>181000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>163300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>157700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>146300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>132800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>119500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>114000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>98400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>80900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>73000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>67600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>63600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>51700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>49700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,31 +4931,34 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>40000</v>
+        <v>42800</v>
       </c>
       <c r="E61" s="3">
-        <v>45000</v>
+        <v>53100</v>
       </c>
       <c r="F61" s="3">
-        <v>55000</v>
+        <v>59100</v>
       </c>
       <c r="G61" s="3">
-        <v>75000</v>
+        <v>70100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>90700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>16400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4877,77 +5020,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14400</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>15200</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>16400</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>17100</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>17700</v>
+        <v>500</v>
       </c>
       <c r="I62" s="3">
-        <v>18600</v>
+        <v>500</v>
       </c>
       <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="K62" s="3">
         <v>18800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>24000</v>
       </c>
       <c r="S62" s="3">
         <v>24000</v>
       </c>
       <c r="T62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="U62" s="3">
         <v>23100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5376,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>230700</v>
+      </c>
+      <c r="E66" s="3">
         <v>241500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>242600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>252400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>255400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>175300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>164900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>151600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>138800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>134300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>127700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>119500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>75600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>72800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>70600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>58300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5574,13 +5742,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>103000</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5854,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-340000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-322900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-306000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-292400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-272300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-249300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-236200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-214000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-200100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-185500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-175700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-165800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-158900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-153400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-147000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-141200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-134200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-125900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-115400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-84500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6210,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E76" s="3">
         <v>152100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>147400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>144200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>144900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>149100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>144800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>142300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>139700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>141100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>142800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>145200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>150200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>150400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>152100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>156600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>119000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>128000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>128100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-95100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-90200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-25900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,31 +6606,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -6462,29 +6661,29 @@
         <v>1000</v>
       </c>
       <c r="T83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
       </c>
       <c r="V83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="W83" s="3">
         <v>1300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>1300</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,83 +7138,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
-      </c>
-      <c r="O89" s="3">
-        <v>4400</v>
       </c>
       <c r="P89" s="3">
         <v>4400</v>
       </c>
       <c r="Q89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R89" s="3">
         <v>3600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7010,8 +7227,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7262,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7051,74 +7272,74 @@
         <v>-500</v>
       </c>
       <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-400</v>
       </c>
       <c r="J91" s="3">
         <v>-400</v>
       </c>
       <c r="K91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-200</v>
       </c>
       <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>-200</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,83 +7527,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>13300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>32200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-8700</v>
       </c>
       <c r="I94" s="3">
         <v>-8700</v>
       </c>
       <c r="J94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-18900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-29900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-200</v>
       </c>
       <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>-200</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,83 +8005,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>73700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>42000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>127600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3">
         <v>29700</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7848,31 +8094,34 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,83 +8183,86 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-57600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>122700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3">
         <v>24600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8018,6 +8270,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E8" s="3">
         <v>102600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>99400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>96800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>85500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>79300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>69700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>53300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>44700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>40800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>23400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17400</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E9" s="3">
         <v>23200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>22400</v>
       </c>
       <c r="F9" s="3">
         <v>22400</v>
       </c>
       <c r="G9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="H9" s="3">
         <v>21000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5800</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>5400</v>
       </c>
       <c r="AB9" s="3">
         <v>5400</v>
       </c>
       <c r="AC9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AD9" s="3">
         <v>5200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5000</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E10" s="3">
         <v>79400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>74400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>72600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>43400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>40000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>33500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>30800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>19200</v>
       </c>
       <c r="X10" s="3">
         <v>19200</v>
       </c>
       <c r="Y10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="Z10" s="3">
         <v>18600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>16900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>15000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12400</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,73 +1097,74 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E12" s="3">
         <v>26300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7800</v>
-      </c>
-      <c r="T12" s="3">
-        <v>7700</v>
       </c>
       <c r="U12" s="3">
         <v>7700</v>
       </c>
       <c r="V12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="W12" s="3">
         <v>7300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8900</v>
-      </c>
-      <c r="X12" s="3">
-        <v>6400</v>
       </c>
       <c r="Y12" s="3">
         <v>6400</v>
@@ -1163,19 +1176,22 @@
         <v>6400</v>
       </c>
       <c r="AB12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AC12" s="3">
         <v>6300</v>
       </c>
       <c r="AD12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AE12" s="3">
         <v>6500</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,13 +1279,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1277,20 +1296,20 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>4300</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1352,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1367,20 +1389,20 @@
         <v>2500</v>
       </c>
       <c r="G15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E17" s="3">
         <v>119500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>115900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>110100</v>
       </c>
-      <c r="G17" s="3">
-        <v>107500</v>
-      </c>
       <c r="H17" s="3">
+        <v>111800</v>
+      </c>
+      <c r="I17" s="3">
         <v>106000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>87100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>82800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>79700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>67000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>39700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>41500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>54100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>35600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>23900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-20400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-26000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,50 +1714,51 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1733,19 +1766,19 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
-      </c>
-      <c r="W20" s="3">
-        <v>200</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
@@ -1760,7 +1793,7 @@
         <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
@@ -1768,121 +1801,127 @@
       <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-11600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-18800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-24400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1000</v>
       </c>
       <c r="F22" s="3">
         <v>1000</v>
       </c>
       <c r="G22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1896,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1935,111 +1974,117 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
       </c>
       <c r="AC22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-25800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2047,19 +2092,19 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -2086,16 +2131,16 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2124,11 +2169,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-25900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-25900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,50 +2816,53 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2801,19 +2870,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-200</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
@@ -2828,7 +2897,7 @@
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
@@ -2836,100 +2905,106 @@
       <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-25900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-25900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E41" s="3">
         <v>82900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>80900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>81700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>107100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>115300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>108300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>102300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>114500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>117800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>79800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>135300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,68 +3441,71 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>71900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>106100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>105200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>97700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>69800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>59700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>63200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>65500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>49400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>49500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>49700</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3432,8 +3521,8 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3444,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E43" s="3">
         <v>54400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>50400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>36700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3559,8 +3654,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3622,80 +3717,83 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E45" s="3">
         <v>17700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,80 +3809,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E46" s="3">
         <v>178500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>183100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>177700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>195900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>196200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>259300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>235500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>225200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>223800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>226800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>222500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>210100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>205100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>199300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>193700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>154400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>161100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>157000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>30800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>35700</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3811,36 +3915,36 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,8 +3960,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3889,80 +3993,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E48" s="3">
         <v>18800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20600</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3978,80 +4085,83 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E49" s="3">
         <v>144700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>146300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>147800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>149500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>152300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8500</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1000</v>
       </c>
       <c r="F52" s="3">
         <v>1000</v>
       </c>
       <c r="G52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>1100</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5900</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>428300</v>
+      </c>
+      <c r="E54" s="3">
         <v>388800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>393600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>389900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>396600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>400300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>324500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>309600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>293900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>278500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>275300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>270500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>264700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>250600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>245600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>241200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>239700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>232300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>191800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>198500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>189600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,35 +4797,38 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4000</v>
       </c>
       <c r="F58" s="3">
         <v>4000</v>
       </c>
       <c r="G58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H58" s="3">
         <v>3900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>3700</v>
       </c>
       <c r="I58" s="3">
         <v>3700</v>
       </c>
       <c r="J58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K58" s="3">
         <v>3600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4756,80 +4889,83 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E59" s="3">
         <v>149200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>148300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>146400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>140500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>122500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>127800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>112300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>107300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>76600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>72400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>66900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>62000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>47500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>37600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>36400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,80 +4981,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>220800</v>
+      </c>
+      <c r="E60" s="3">
         <v>186500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>187100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>182400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>181000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>163300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>157700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>146300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>132800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>119500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>114000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>107300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>98400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>80900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>73000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>67600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>63600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>49700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>47000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,35 +5073,38 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E61" s="3">
         <v>42800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>70100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>90700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5023,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5041,7 +5186,7 @@
         <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>500</v>
@@ -5050,53 +5195,53 @@
         <v>500</v>
       </c>
       <c r="K62" s="3">
+        <v>500</v>
+      </c>
+      <c r="L62" s="3">
         <v>18800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>24000</v>
       </c>
       <c r="T62" s="3">
         <v>24000</v>
       </c>
       <c r="U62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="V62" s="3">
         <v>23100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19500</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>261700</v>
+      </c>
+      <c r="E66" s="3">
         <v>230700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>241500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>242600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>252400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>255400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>175300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>164900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>138800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>134300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>127700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>119500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>95500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>87600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>75600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>72800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>61500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5745,13 +5912,13 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>103000</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-354400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-340000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-322900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-306000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-292400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-272300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-249300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-236200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-214000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-200100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-185500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-175700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-165800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-158900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-153400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-147000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-141200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-134200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-125900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-115400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-84500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>166600</v>
+      </c>
+      <c r="E76" s="3">
         <v>158100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>152100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>147400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>144200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>144900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>149100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>144800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>142300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>139700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>141100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>142800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>145200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>150200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>150400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>152100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>156600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>119000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>128000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>128100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-95100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-90200</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-25900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,19 +6804,20 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E83" s="3">
         <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
@@ -6628,13 +6826,13 @@
         <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
       </c>
       <c r="K83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>1000</v>
@@ -6664,29 +6862,29 @@
         <v>1000</v>
       </c>
       <c r="U83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
       </c>
       <c r="W83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>1300</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,86 +7354,89 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>9000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
-      </c>
-      <c r="P89" s="3">
-        <v>4400</v>
       </c>
       <c r="Q89" s="3">
         <v>4400</v>
       </c>
       <c r="R89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S89" s="3">
         <v>3600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7230,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,86 +7482,87 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-500</v>
+        <v>-900</v>
       </c>
       <c r="E91" s="3">
         <v>-500</v>
       </c>
       <c r="F91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-200</v>
       </c>
       <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>-200</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,86 +7756,89 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E94" s="3">
         <v>3300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>32200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-8700</v>
       </c>
       <c r="J94" s="3">
         <v>-8700</v>
       </c>
       <c r="K94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>25900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-50200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-200</v>
       </c>
       <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>-200</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7619,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,8 +7911,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,86 +8250,89 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-19800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>73700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>42000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>127600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3">
         <v>29700</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8097,8 +8342,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8186,86 +8434,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-57600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>122700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3">
         <v>24600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8273,6 +8524,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>109300</v>
+      </c>
+      <c r="E8" s="3">
         <v>107100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>102600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>99400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>96800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>85500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>79300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>69700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>53300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>44700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17400</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E9" s="3">
         <v>23400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>22400</v>
       </c>
       <c r="G9" s="3">
         <v>22400</v>
       </c>
       <c r="H9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="I9" s="3">
         <v>21000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>5400</v>
       </c>
       <c r="AC9" s="3">
         <v>5400</v>
       </c>
       <c r="AD9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AE9" s="3">
         <v>5200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5000</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E10" s="3">
         <v>83700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>79400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>77000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>74400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>72600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>65300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>61100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>58300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>43400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>40000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>36800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>30800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22300</v>
-      </c>
-      <c r="X10" s="3">
-        <v>19200</v>
       </c>
       <c r="Y10" s="3">
         <v>19200</v>
       </c>
       <c r="Z10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AA10" s="3">
         <v>18600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>16900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>12400</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,76 +1111,77 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E12" s="3">
         <v>24700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
-      </c>
-      <c r="U12" s="3">
-        <v>7700</v>
       </c>
       <c r="V12" s="3">
         <v>7700</v>
       </c>
       <c r="W12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="X12" s="3">
         <v>7300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8900</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>6400</v>
       </c>
       <c r="Z12" s="3">
         <v>6400</v>
@@ -1179,19 +1193,22 @@
         <v>6400</v>
       </c>
       <c r="AC12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AD12" s="3">
         <v>6300</v>
       </c>
       <c r="AE12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AF12" s="3">
         <v>6500</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,37 +1299,40 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1392,20 +1415,20 @@
         <v>2500</v>
       </c>
       <c r="H15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E17" s="3">
         <v>117700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>119500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>115900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>110100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>111800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>106000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>94200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>87100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>82800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>79700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>76000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>67000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>41500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>54100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>35600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>23900</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,53 +1748,54 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1769,19 +1803,19 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
@@ -1796,7 +1830,7 @@
         <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
@@ -1804,127 +1838,133 @@
       <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1000</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
       </c>
       <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1938,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1977,137 +2017,143 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -2134,16 +2180,16 @@
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2172,11 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,53 +2886,56 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2873,19 +2943,19 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
@@ -2900,7 +2970,7 @@
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
@@ -2908,103 +2978,109 @@
       <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,83 +3438,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E41" s="3">
         <v>86400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>82900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>79900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>95100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>107100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>115300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>108300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>102300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>114500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>117800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>137400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>135300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>18800</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,71 +3531,74 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>44600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>71900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>106100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>99100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>92900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>105200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>69800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>63200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>65500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>49400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>49500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>49700</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,8 +3614,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3536,83 +3626,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E43" s="3">
         <v>84000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>54400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>36700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>35800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>26700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9200</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3657,8 +3753,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3720,83 +3816,86 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E45" s="3">
         <v>20200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,83 +3911,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>207500</v>
+      </c>
+      <c r="E46" s="3">
         <v>210200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>178500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>183100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>177700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>195900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>196200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>259300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>246400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>235500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>225200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>223800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>226800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>222500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>210100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>205100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>199300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>193700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>154400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>161100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>157000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>30800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>35700</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3918,36 +4023,36 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4068,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3996,83 +4101,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E48" s="3">
         <v>22300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,83 +4196,86 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E49" s="3">
         <v>143200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>144700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>146300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>147800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>149500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>152300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8500</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4373,74 +4493,74 @@
         <v>1000</v>
       </c>
       <c r="E52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1000</v>
       </c>
       <c r="G52" s="3">
         <v>1000</v>
       </c>
       <c r="H52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I52" s="3">
         <v>1100</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>19700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,83 +4671,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>424700</v>
+      </c>
+      <c r="E54" s="3">
         <v>428300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>388800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>393600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>389900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>396600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>400300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>324500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>309600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>293900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>278500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>275300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>270500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>264700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>250600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>245600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>241200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>239700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>232300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>191800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>198500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>189600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,83 +4838,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,38 +4931,41 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4000</v>
       </c>
       <c r="G58" s="3">
         <v>4000</v>
       </c>
       <c r="H58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I58" s="3">
         <v>3900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>3700</v>
       </c>
       <c r="J58" s="3">
         <v>3700</v>
       </c>
       <c r="K58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L58" s="3">
         <v>3600</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4892,83 +5026,86 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E59" s="3">
         <v>178600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>149200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>148300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>146400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>140500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>122500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>115900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>127800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>112300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>107300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>102600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>95500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>76600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>66900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>62000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>47500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>41000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>37600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>36400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,83 +5121,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>214100</v>
+      </c>
+      <c r="E60" s="3">
         <v>220800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>186500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>187100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>182400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>181000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>163300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>157700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>146300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>132800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>119500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>114000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>107300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>98400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>80900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>73000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>67600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>63600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>51700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>49700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>47000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,38 +5216,41 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>70100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>90700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5168,13 +5311,16 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
@@ -5189,7 +5335,7 @@
         <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>500</v>
@@ -5198,53 +5344,53 @@
         <v>500</v>
       </c>
       <c r="L62" s="3">
+        <v>500</v>
+      </c>
+      <c r="M62" s="3">
         <v>18800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>24000</v>
       </c>
       <c r="U62" s="3">
         <v>24000</v>
       </c>
       <c r="V62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="W62" s="3">
         <v>23100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>19500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,83 +5691,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E66" s="3">
         <v>261700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>230700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>241500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>242600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>252400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>255400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>175300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>151600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>138800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>134300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>127700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>119500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>95500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>87600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>75600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>72800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5915,13 +6083,13 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>103000</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6201,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-365600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-354400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-340000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-322900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-306000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-292400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-272300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-249300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-236200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-226000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-214000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-185500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-175700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-165800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-158900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-153400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-147000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-141200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-134200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-125900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-115400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-84500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,83 +6581,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E76" s="3">
         <v>166600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>158100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>152100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>147400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>144200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>144900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>149100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>144800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>142300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>139700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>141100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>142800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>145200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>148000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>150200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>150400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>152100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>156600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>119000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>128000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>128100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-95100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-90200</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6814,13 +7013,13 @@
         <v>1300</v>
       </c>
       <c r="E83" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F83" s="3">
         <v>1200</v>
       </c>
       <c r="G83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H83" s="3">
         <v>1100</v>
@@ -6829,13 +7028,13 @@
         <v>1100</v>
       </c>
       <c r="J83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
       </c>
       <c r="L83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M83" s="3">
         <v>1000</v>
@@ -6865,29 +7064,29 @@
         <v>1000</v>
       </c>
       <c r="V83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="W83" s="3">
         <v>1100</v>
       </c>
       <c r="X83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="Y83" s="3">
         <v>1300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>1300</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1000</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,89 +7571,92 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>4400</v>
       </c>
       <c r="R89" s="3">
         <v>4400</v>
       </c>
       <c r="S89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T89" s="3">
         <v>3600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,89 +7703,90 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-500</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-200</v>
       </c>
       <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Z91" s="3">
+        <v>-200</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,89 +7986,92 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>20100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>32200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-8700</v>
       </c>
       <c r="K94" s="3">
         <v>-8700</v>
       </c>
       <c r="L94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="M94" s="3">
         <v>-18900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>25900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-50200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-200</v>
       </c>
       <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Z94" s="3">
+        <v>-200</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7914,8 +8148,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,89 +8496,92 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-19800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>73700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>42000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>127600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3">
         <v>29700</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8374,8 +8623,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8437,89 +8686,92 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E102" s="3">
         <v>3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-57600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>122700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3">
         <v>24600</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E8" s="3">
         <v>109300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>107100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>99400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>96800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>85500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>79300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>75200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>69700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>53300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>44700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>40800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>23400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>22300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17400</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E9" s="3">
         <v>24800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>22400</v>
       </c>
       <c r="H9" s="3">
         <v>22400</v>
       </c>
       <c r="I9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="J9" s="3">
         <v>21000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5800</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>5400</v>
       </c>
       <c r="AD9" s="3">
         <v>5400</v>
       </c>
       <c r="AE9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AF9" s="3">
         <v>5200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5000</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E10" s="3">
         <v>84500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>77000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>72600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>65300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>54300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>50000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>43400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>33500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>30800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>27700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22300</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>19200</v>
       </c>
       <c r="Z10" s="3">
         <v>19200</v>
       </c>
       <c r="AA10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AB10" s="3">
         <v>18600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>16900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>15000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12400</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,79 +1125,80 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E12" s="3">
         <v>23200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
-      </c>
-      <c r="V12" s="3">
-        <v>7700</v>
       </c>
       <c r="W12" s="3">
         <v>7700</v>
       </c>
       <c r="X12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Y12" s="3">
         <v>7300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8900</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>6400</v>
       </c>
       <c r="AA12" s="3">
         <v>6400</v>
@@ -1196,19 +1210,22 @@
         <v>6400</v>
       </c>
       <c r="AD12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AE12" s="3">
         <v>6300</v>
       </c>
       <c r="AF12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AG12" s="3">
         <v>6500</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,40 +1319,43 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1397,13 +1417,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
         <v>2500</v>
@@ -1418,20 +1441,20 @@
         <v>2500</v>
       </c>
       <c r="I15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J15" s="3">
         <v>2400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E17" s="3">
         <v>120500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>117700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>119500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>115900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>110100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>111800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>106000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>94200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>87100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>82800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>79700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>41500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>54100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>35600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>28700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>23900</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,56 +1782,57 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1806,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
@@ -1833,7 +1867,7 @@
         <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
@@ -1841,133 +1875,139 @@
       <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-14200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>1000</v>
       </c>
       <c r="I22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1981,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -2020,143 +2060,149 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>200</v>
       </c>
       <c r="AE22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-25800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>300</v>
       </c>
       <c r="G24" s="3">
+        <v>300</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
@@ -2183,16 +2229,16 @@
         <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2221,11 +2267,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,56 +2956,59 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2946,19 +3016,19 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
@@ -2973,7 +3043,7 @@
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
@@ -2981,106 +3051,112 @@
       <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,86 +3525,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E41" s="3">
         <v>100900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>79900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>95100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>107100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>115300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>108300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>102300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>114500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>117800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>137400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>135300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18800</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,74 +3621,77 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>44600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>71900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>106100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>99100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>92900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>77000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>105200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>97700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>69800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>59700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>63200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>65500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>49400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>49500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>49700</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3617,8 +3707,8 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3629,86 +3719,89 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E43" s="3">
         <v>64800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>84000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>54400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>36700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3756,8 +3852,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3819,86 +3915,89 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E45" s="3">
         <v>21800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>17700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>23200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>18300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,86 +4013,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>207800</v>
+      </c>
+      <c r="E46" s="3">
         <v>207500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>210200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>178500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>183100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>177700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>195900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>196200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>259300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>246400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>235500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>225200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>223800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>226800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>222500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>210100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>205100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>199300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>193700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>154400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>161100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>157000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>30800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>35700</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4026,36 +4131,36 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4176,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4104,86 +4209,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E48" s="3">
         <v>21900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20600</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,86 +4307,89 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>140600</v>
+      </c>
+      <c r="E49" s="3">
         <v>141900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>143200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>144700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>146300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>147800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>149500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>152300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,86 +4601,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
         <v>1000</v>
       </c>
       <c r="F52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G52" s="3">
         <v>1100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>1000</v>
       </c>
       <c r="I52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J52" s="3">
         <v>1100</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>19700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,86 +4797,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>422900</v>
+      </c>
+      <c r="E54" s="3">
         <v>424700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>428300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>388800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>393600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>389900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>396600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>400300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>324500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>309600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>293900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>278500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>275300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>270500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>264700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>250600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>245600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>241200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>239700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>232300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>191800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>198500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>189600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,86 +4969,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,41 +5065,44 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4000</v>
       </c>
       <c r="H58" s="3">
         <v>4000</v>
       </c>
       <c r="I58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J58" s="3">
         <v>3900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3700</v>
       </c>
       <c r="K58" s="3">
         <v>3700</v>
       </c>
       <c r="L58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M58" s="3">
         <v>3600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5029,86 +5163,89 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>171100</v>
+      </c>
+      <c r="E59" s="3">
         <v>174000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>178600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>149200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>148300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>146400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>140500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>122500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>115900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>127800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>112300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>107300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>102600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>76600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>66900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>62000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>47500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>44500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>37600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>36400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5124,86 +5261,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="E60" s="3">
         <v>214100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>220800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>186500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>187100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>181000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>163300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>157700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>146300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>132800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>119500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>114000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>107300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>98400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>80900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>73000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>67600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>63600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>51700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>49700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>47000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5219,41 +5359,44 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E61" s="3">
         <v>34000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>42800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>70100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>90700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5323,7 +5469,7 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
@@ -5338,7 +5484,7 @@
         <v>400</v>
       </c>
       <c r="J62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K62" s="3">
         <v>500</v>
@@ -5347,53 +5493,53 @@
         <v>500</v>
       </c>
       <c r="M62" s="3">
+        <v>500</v>
+      </c>
+      <c r="N62" s="3">
         <v>18800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>24000</v>
       </c>
       <c r="V62" s="3">
         <v>24000</v>
       </c>
       <c r="W62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="X62" s="3">
         <v>23100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>23600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,86 +5849,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>238400</v>
+      </c>
+      <c r="E66" s="3">
         <v>249300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>261700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>230700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>241500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>242600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>252400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>255400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>175300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>151600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>138800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>134300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>127700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>119500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>95500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>87600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>75600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>72800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6086,13 +6254,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>103000</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,86 +6375,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-377600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-365600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-354400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-340000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-322900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-306000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-292400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-272300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-249300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-236200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-226000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-214000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-185500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-175700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-165800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-158900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-153400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-147000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-141200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-134200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-125900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-115400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-84500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,86 +6767,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E76" s="3">
         <v>175300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>166600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>158100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>152100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>147400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>144200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>144900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>144800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>142300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>139700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>141100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>142800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>145200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>150200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>150400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>152100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>156600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>119000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>128000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>128100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-95100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-90200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,25 +7202,26 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1300</v>
       </c>
       <c r="F83" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G83" s="3">
         <v>1200</v>
       </c>
       <c r="H83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
@@ -7031,13 +7230,13 @@
         <v>1100</v>
       </c>
       <c r="K83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
       </c>
       <c r="M83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N83" s="3">
         <v>1000</v>
@@ -7067,29 +7266,29 @@
         <v>1000</v>
       </c>
       <c r="W83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="X83" s="3">
         <v>1100</v>
       </c>
       <c r="Y83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="Z83" s="3">
         <v>1300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>1300</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,92 +7788,95 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>18100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2500</v>
-      </c>
-      <c r="R89" s="3">
-        <v>4400</v>
       </c>
       <c r="S89" s="3">
         <v>4400</v>
       </c>
       <c r="T89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U89" s="3">
         <v>3600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,92 +7924,93 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-500</v>
       </c>
       <c r="G91" s="3">
         <v>-500</v>
       </c>
       <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-400</v>
       </c>
       <c r="M91" s="3">
         <v>-400</v>
       </c>
       <c r="N91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-200</v>
       </c>
       <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
+      <c r="AA91" s="3">
+        <v>-200</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,92 +8216,95 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>32200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-8700</v>
       </c>
       <c r="L94" s="3">
         <v>-8700</v>
       </c>
       <c r="M94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N94" s="3">
         <v>-18900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>25900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-200</v>
       </c>
       <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
+      <c r="AA94" s="3">
+        <v>-200</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8151,8 +8385,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,92 +8742,95 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>42000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>127600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD100" s="3">
         <v>29700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8594,8 +8840,11 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8626,8 +8875,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8689,92 +8938,95 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-57600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>122700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3">
         <v>24600</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8782,6 +9034,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E8" s="3">
         <v>115600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>111800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>109300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>102600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>99400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>96800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>85500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>79300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>61400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>53300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>49100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>44700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>40800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>33700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>17400</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E9" s="3">
         <v>25800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>22400</v>
       </c>
       <c r="J9" s="3">
         <v>22400</v>
       </c>
       <c r="K9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="L9" s="3">
         <v>21000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5800</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>5400</v>
       </c>
       <c r="AF9" s="3">
         <v>5400</v>
       </c>
       <c r="AG9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AH9" s="3">
         <v>5200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5000</v>
       </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E10" s="3">
         <v>89800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>86800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>84500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>83700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>79400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>72600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>61100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>58300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>54300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>50000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>40000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>36800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>33500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>30800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>27700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22300</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>19200</v>
       </c>
       <c r="AB10" s="3">
         <v>19200</v>
       </c>
       <c r="AC10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AD10" s="3">
         <v>18600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>16900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>15000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>12400</v>
       </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,85 +1152,86 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E12" s="3">
         <v>25100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7800</v>
-      </c>
-      <c r="X12" s="3">
-        <v>7700</v>
       </c>
       <c r="Y12" s="3">
         <v>7700</v>
       </c>
       <c r="Z12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AA12" s="3">
         <v>7300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8900</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>6400</v>
       </c>
       <c r="AC12" s="3">
         <v>6400</v>
@@ -1230,19 +1243,22 @@
         <v>6400</v>
       </c>
       <c r="AF12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AG12" s="3">
         <v>6300</v>
       </c>
       <c r="AH12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AI12" s="3">
         <v>6500</v>
       </c>
-      <c r="AI12" s="3" t="s">
+      <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,46 +1358,49 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>1700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>1700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1443,19 +1462,22 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2500</v>
       </c>
       <c r="G15" s="3">
         <v>2500</v>
@@ -1470,20 +1492,20 @@
         <v>2500</v>
       </c>
       <c r="K15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1544,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E17" s="3">
         <v>123000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>124100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>120500</v>
       </c>
-      <c r="G17" s="3">
-        <v>117700</v>
-      </c>
       <c r="H17" s="3">
+        <v>117800</v>
+      </c>
+      <c r="I17" s="3">
         <v>119500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>115900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>110100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>111800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>106000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>94200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>87100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>82800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>79700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>76000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>63000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>55900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>41500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>54100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>35600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>28700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>26200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>23900</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,62 +1849,63 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1880,19 +1913,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>200</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
@@ -1907,7 +1940,7 @@
         <v>200</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
@@ -1915,112 +1948,118 @@
       <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="T21" s="3">
         <v>-8700</v>
       </c>
-      <c r="H21" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-12800</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2028,32 +2067,32 @@
         <v>800</v>
       </c>
       <c r="E22" s="3">
+        <v>800</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1000</v>
       </c>
       <c r="J22" s="3">
         <v>1000</v>
       </c>
       <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2067,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -2106,155 +2145,161 @@
         <v>100</v>
       </c>
       <c r="AE22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF22" s="3">
         <v>200</v>
       </c>
       <c r="AG22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-25800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
@@ -2281,16 +2326,16 @@
         <v>100</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2319,11 +2364,14 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,62 +3095,65 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3092,19 +3161,19 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-200</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
@@ -3119,7 +3188,7 @@
         <v>-200</v>
       </c>
       <c r="AF32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
@@ -3127,112 +3196,118 @@
       <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,92 +3698,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E41" s="3">
         <v>90600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>101500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>86400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>80900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>79900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>107100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>115300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>102300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>114500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>117800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>79800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>137400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>135300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>18800</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3714,8 +3800,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3726,68 +3815,68 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>71900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>106100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>99100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>92900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>77000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>105200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>97700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>69800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>59700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>63200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>65500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>49400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>49500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>49700</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3892,8 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -3815,92 +3904,95 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E43" s="3">
         <v>63500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>64800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>84000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>54400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>36700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>26700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>9200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3916,8 +4008,11 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3954,8 +4049,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4017,92 +4112,95 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E45" s="3">
         <v>25200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>18300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4118,92 +4216,95 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>237200</v>
+      </c>
+      <c r="E46" s="3">
         <v>195000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>207800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>210200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>178500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>177700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>195900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>196200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>259300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>235500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>225200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>223800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>226800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>222500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>210100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>205100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>199300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>193700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>154400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>161100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>157000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>30800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>35700</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4320,11 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4242,36 +4346,36 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1500</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4287,8 +4391,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4320,92 +4424,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E48" s="3">
         <v>20100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>25100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20600</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4421,92 +4528,95 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E49" s="3">
         <v>209100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>140600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>141900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>143200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>144700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>146300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>147800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>149500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>152300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4522,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,92 +4840,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1000</v>
       </c>
       <c r="G52" s="3">
         <v>1000</v>
       </c>
       <c r="H52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1000</v>
       </c>
       <c r="J52" s="3">
         <v>1000</v>
       </c>
       <c r="K52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="L52" s="3">
         <v>1100</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>19700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,92 +5048,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>523100</v>
+      </c>
+      <c r="E54" s="3">
         <v>481400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>422900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>424700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>428300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>388800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>393600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>389900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>396600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>400300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>324500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>309600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>293900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>278500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>275300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>270500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>264700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>250600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>245600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>241200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>239700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>232300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>191800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>198500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>189600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>66200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,92 +5230,93 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E57" s="3">
         <v>9400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5202,47 +5332,50 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4000</v>
       </c>
       <c r="J58" s="3">
         <v>4000</v>
       </c>
       <c r="K58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L58" s="3">
         <v>3900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3700</v>
       </c>
       <c r="M58" s="3">
         <v>3700</v>
       </c>
       <c r="N58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O58" s="3">
         <v>3600</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5303,92 +5436,95 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>205600</v>
+      </c>
+      <c r="E59" s="3">
         <v>172600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>171100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>174000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>178600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>149200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>148300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>146400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>140500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>122500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>115900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>109100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>127800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>112300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>107300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>102600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>95500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>76600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>66900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>62000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>47500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>44500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>41000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>37600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>36400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5404,92 +5540,95 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>256300</v>
+      </c>
+      <c r="E60" s="3">
         <v>219100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>208600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>214100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>220800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>186500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>187100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>182400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>181000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>157700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>146300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>132800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>119500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>114000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>107300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>98400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>80900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>73000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>67600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>63600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>51700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>49700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>47000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>39400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5505,47 +5644,50 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E61" s="3">
         <v>56800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>70100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>90700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5606,22 +5748,25 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E62" s="3">
         <v>10500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
@@ -5636,7 +5781,7 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>500</v>
@@ -5645,53 +5790,53 @@
         <v>500</v>
       </c>
       <c r="O62" s="3">
+        <v>500</v>
+      </c>
+      <c r="P62" s="3">
         <v>18800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23200</v>
-      </c>
-      <c r="W62" s="3">
-        <v>24000</v>
       </c>
       <c r="X62" s="3">
         <v>24000</v>
       </c>
       <c r="Y62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="Z62" s="3">
         <v>23100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>23600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19500</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5707,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,92 +6164,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E66" s="3">
         <v>287300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>238400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>249300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>261700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>230700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>241500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>242600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>252400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>255400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>175300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>164900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>151600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>138800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>134300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>127700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>119500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>102700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>95500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>90800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>75600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>72800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>70600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>58300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>57900</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6428,13 +6595,13 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>103000</v>
       </c>
       <c r="AD70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
@@ -6451,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,92 +6722,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-397700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-387000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-377600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-365600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-354400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-340000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-322900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-306000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-292400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-272300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-249300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-236200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-226000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-214000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-185500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-175700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-165800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-158900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-153400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-147000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-141200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-134200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-125900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-115400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-84500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6653,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,92 +7138,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>203400</v>
+      </c>
+      <c r="E76" s="3">
         <v>194100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>184600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>175300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>166600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>158100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>152100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>147400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>144200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>144900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>149100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>144800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>142300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>139700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>141100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>142800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>145200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>148000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>150200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>150400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>152100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>156600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>119000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>128000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>128100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-95100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-90200</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7057,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
         <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G83" s="3">
         <v>1300</v>
       </c>
       <c r="H83" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I83" s="3">
         <v>1200</v>
       </c>
       <c r="J83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="K83" s="3">
         <v>1100</v>
@@ -7435,13 +7633,13 @@
         <v>1100</v>
       </c>
       <c r="M83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="N83" s="3">
         <v>900</v>
       </c>
       <c r="O83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P83" s="3">
         <v>1000</v>
@@ -7471,29 +7669,29 @@
         <v>1000</v>
       </c>
       <c r="Y83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Z83" s="3">
         <v>1100</v>
       </c>
       <c r="AA83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="AB83" s="3">
         <v>1300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3">
+        <v>1300</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7503,8 +7701,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,98 +8221,101 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2500</v>
-      </c>
-      <c r="T89" s="3">
-        <v>4400</v>
       </c>
       <c r="U89" s="3">
         <v>4400</v>
       </c>
       <c r="V89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="W89" s="3">
         <v>3600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8109,8 +8325,11 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,98 +8365,99 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-500</v>
       </c>
       <c r="I91" s="3">
         <v>-500</v>
       </c>
       <c r="J91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-400</v>
       </c>
       <c r="O91" s="3">
         <v>-400</v>
       </c>
       <c r="P91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
       </c>
       <c r="T91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-200</v>
       </c>
       <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>-200</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8247,8 +8467,11 @@
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,98 +8675,101 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>20100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>32200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-8700</v>
       </c>
       <c r="N94" s="3">
         <v>-8700</v>
       </c>
       <c r="O94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="P94" s="3">
         <v>-18900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>25900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-29900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-50200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-200</v>
       </c>
       <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
+      <c r="AC94" s="3">
+        <v>-200</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8550,8 +8779,11 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8625,8 +8858,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8688,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,98 +9233,101 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E100" s="3">
         <v>28800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>73700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>42000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>127600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3">
         <v>29700</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9092,8 +9337,11 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9130,8 +9378,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9193,98 +9441,101 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>38000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>122700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3">
         <v>24600</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9292,6 +9543,9 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>SPT</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E8" s="3">
         <v>120900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>115600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>111800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>109300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>107100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>102600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>99400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>96800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>93600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>85500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>79300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>65300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>61400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>53300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>49100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>44700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>40800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>30500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>22300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E9" s="3">
         <v>27100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24900</v>
       </c>
-      <c r="G9" s="3">
-        <v>24800</v>
-      </c>
       <c r="H9" s="3">
+        <v>24400</v>
+      </c>
+      <c r="I9" s="3">
         <v>23400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>22400</v>
       </c>
       <c r="K9" s="3">
         <v>22400</v>
       </c>
       <c r="L9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="M9" s="3">
         <v>21000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5800</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>5400</v>
       </c>
       <c r="AG9" s="3">
         <v>5400</v>
       </c>
       <c r="AH9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AI9" s="3">
         <v>5200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E10" s="3">
         <v>93700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>89800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>86800</v>
       </c>
-      <c r="G10" s="3">
-        <v>84500</v>
-      </c>
       <c r="H10" s="3">
+        <v>84900</v>
+      </c>
+      <c r="I10" s="3">
         <v>83700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>79400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>72600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>61100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>54300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>50000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>36800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>33500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>30800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22300</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>19200</v>
       </c>
       <c r="AC10" s="3">
         <v>19200</v>
       </c>
       <c r="AD10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="AE10" s="3">
         <v>18600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>16900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,88 +1166,89 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E12" s="3">
         <v>26100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7800</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>7700</v>
       </c>
       <c r="Z12" s="3">
         <v>7700</v>
       </c>
       <c r="AA12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AB12" s="3">
         <v>7300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8900</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>6400</v>
       </c>
       <c r="AD12" s="3">
         <v>6400</v>
@@ -1246,19 +1260,22 @@
         <v>6400</v>
       </c>
       <c r="AG12" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="AH12" s="3">
         <v>6300</v>
       </c>
       <c r="AI12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ12" s="3" t="s">
+      <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,49 +1378,52 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1700</v>
+        <v>-500</v>
       </c>
       <c r="E14" s="3">
         <v>1700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>1700</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1465,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,13 +1497,13 @@
         <v>3300</v>
       </c>
       <c r="E15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="3">
         <v>2900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2500</v>
       </c>
       <c r="H15" s="3">
         <v>2500</v>
@@ -1495,20 +1518,20 @@
         <v>2500</v>
       </c>
       <c r="L15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M15" s="3">
         <v>2400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1100</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E17" s="3">
         <v>130000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>123000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>124100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>120500</v>
       </c>
       <c r="H17" s="3">
         <v>117800</v>
       </c>
       <c r="I17" s="3">
+        <v>117800</v>
+      </c>
+      <c r="J17" s="3">
         <v>119500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>115900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>110100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>111800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>106000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>94200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>87100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>82800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>79700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>76000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>67000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>55900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>43100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>40600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>39700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>41500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>54100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>31500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>35600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>28700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>26200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-11200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,65 +1883,66 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1916,19 +1950,19 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
@@ -1943,7 +1977,7 @@
         <v>200</v>
       </c>
       <c r="AG20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
@@ -1951,151 +1985,157 @@
       <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-8900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-8800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-13500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
         <v>800</v>
       </c>
       <c r="F22" s="3">
+        <v>800</v>
+      </c>
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>1000</v>
       </c>
       <c r="L22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -2109,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -2148,161 +2188,167 @@
         <v>100</v>
       </c>
       <c r="AF22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>200</v>
       </c>
       <c r="AH22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AJ22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-25800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
@@ -2329,16 +2375,16 @@
         <v>100</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
       <c r="Z24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2367,11 +2413,14 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,65 +3165,68 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3164,19 +3234,19 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
@@ -3191,7 +3261,7 @@
         <v>-200</v>
       </c>
       <c r="AG32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
@@ -3199,115 +3269,121 @@
       <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,95 +3785,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E41" s="3">
         <v>95300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>90600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>86400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>69200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>78400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>79900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>95100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>68600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>81700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>107100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>115300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>102300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>114500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>117800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>79800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>137400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>135300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18800</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3890,11 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3818,68 +3908,68 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>71900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>106100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>99100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>92900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>77000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>105200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>97700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>69800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>59700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>63200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>65500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>49400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>49500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>49700</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3895,8 +3985,8 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -3907,95 +3997,98 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E43" s="3">
         <v>101000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>64800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>84000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>54400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>36700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>26700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9200</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4011,8 +4104,11 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4052,8 +4148,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4115,95 +4211,98 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E45" s="3">
         <v>27000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,95 +4318,98 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>225900</v>
+      </c>
+      <c r="E46" s="3">
         <v>237200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>195000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>207500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>210200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>178500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>183100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>177700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>195900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>196200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>259300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>235500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>225200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>223800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>226800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>222500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>210100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>205100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>199300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>193700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>154400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>161100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>157000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>30800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>35700</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4323,8 +4425,11 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,36 +4454,36 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4499,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4427,95 +4532,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E48" s="3">
         <v>19700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>24000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20600</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,95 +4639,98 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E49" s="3">
         <v>206900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>209100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>140600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>141900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>143200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>144700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>146300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>147800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>149500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>152300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8500</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,95 +4960,98 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>1000</v>
       </c>
       <c r="I52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1000</v>
       </c>
       <c r="K52" s="3">
         <v>1000</v>
       </c>
       <c r="L52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M52" s="3">
         <v>1100</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>19700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5900</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,95 +5174,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>508600</v>
+      </c>
+      <c r="E54" s="3">
         <v>523100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>481400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>422900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>424700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>428300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>388800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>393600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>389900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>396600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>400300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>324500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>309600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>278500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>275300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>270500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>264700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>250600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>245600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>241200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>239700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>232300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>191800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>198500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>189600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>66200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,95 +5361,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E57" s="3">
         <v>10100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2000</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5335,8 +5466,11 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5344,41 +5478,41 @@
         <v>2700</v>
       </c>
       <c r="E58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>4000</v>
       </c>
       <c r="K58" s="3">
         <v>4000</v>
       </c>
       <c r="L58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M58" s="3">
         <v>3900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3700</v>
       </c>
       <c r="N58" s="3">
         <v>3700</v>
       </c>
       <c r="O58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5439,95 +5573,98 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>194300</v>
+      </c>
+      <c r="E59" s="3">
         <v>205600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>172600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>171100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>174000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>178600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>149200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>146400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>140500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>122500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>115900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>109100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>127800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>112300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>107300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>102600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>95500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>76600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>72400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>66900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>62000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>47500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>44500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>41000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>37600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>36400</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5543,95 +5680,98 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>237100</v>
+      </c>
+      <c r="E60" s="3">
         <v>256300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>219100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>208600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>186500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>187100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>182400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>181000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>157700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>146300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>132800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>119500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>114000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>107300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>98400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>80900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>73000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>67600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>63600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>51700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>49700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>47000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>43100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>39400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38400</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5647,50 +5787,53 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E61" s="3">
         <v>52100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>70100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>90700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5751,25 +5894,28 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E62" s="3">
         <v>10600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
       </c>
       <c r="H62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
@@ -5784,7 +5930,7 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>500</v>
@@ -5793,53 +5939,53 @@
         <v>500</v>
       </c>
       <c r="P62" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>18800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23200</v>
-      </c>
-      <c r="X62" s="3">
-        <v>24000</v>
       </c>
       <c r="Y62" s="3">
         <v>24000</v>
       </c>
       <c r="Z62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AA62" s="3">
         <v>23100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>23600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>19500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,95 +6322,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>293400</v>
+      </c>
+      <c r="E66" s="3">
         <v>319600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>287300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>238400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>249300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>261700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>230700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>241500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>242600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>252400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>255400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>175300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>151600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>138800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>134300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>127700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>119500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>95500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>87600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>75600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>72800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>70600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>58300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6598,13 +6766,13 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>103000</v>
       </c>
       <c r="AE70" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="AF70" s="3">
         <v>0</v>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,95 +6896,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-404000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-397700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-387000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-377600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-365600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-354400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-340000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-322900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-306000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-292400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-272300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-249300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-236200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-226000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-214000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-185500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-175700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-165800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-158900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-153400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-147000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-141200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-134200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-125900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-115400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-89500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-84500</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,95 +7324,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>215200</v>
+      </c>
+      <c r="E76" s="3">
         <v>203400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>194100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>184600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>175300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>166600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>158100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>152100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>147400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>144200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>144900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>149100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>144800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>142300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>139700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>141100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>142800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>145200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>148000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>150200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>150400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>152100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>156600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>119000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>128000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>128100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-95100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-90200</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,34 +7798,35 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1400</v>
       </c>
       <c r="F83" s="3">
         <v>1400</v>
       </c>
       <c r="G83" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H83" s="3">
         <v>1300</v>
       </c>
       <c r="I83" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J83" s="3">
         <v>1200</v>
       </c>
       <c r="K83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="L83" s="3">
         <v>1100</v>
@@ -7636,13 +7835,13 @@
         <v>1100</v>
       </c>
       <c r="N83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="O83" s="3">
         <v>900</v>
       </c>
       <c r="P83" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Q83" s="3">
         <v>1000</v>
@@ -7672,29 +7871,29 @@
         <v>1000</v>
       </c>
       <c r="Z83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AA83" s="3">
         <v>1100</v>
       </c>
       <c r="AB83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="AC83" s="3">
         <v>1300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>1300</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1000</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7704,8 +7903,11 @@
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,101 +8438,104 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E89" s="3">
         <v>10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2500</v>
-      </c>
-      <c r="U89" s="3">
-        <v>4400</v>
       </c>
       <c r="V89" s="3">
         <v>4400</v>
       </c>
       <c r="W89" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X89" s="3">
         <v>3600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8328,8 +8545,11 @@
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8586,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8375,92 +8596,92 @@
         <v>-1100</v>
       </c>
       <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
       </c>
       <c r="J91" s="3">
         <v>-500</v>
       </c>
       <c r="K91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-400</v>
       </c>
       <c r="P91" s="3">
         <v>-400</v>
       </c>
       <c r="Q91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-300</v>
       </c>
       <c r="U91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-200</v>
       </c>
       <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
+      <c r="AD91" s="3">
+        <v>-200</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8470,8 +8691,11 @@
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,101 +8905,104 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-51100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>32200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-101400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-8700</v>
       </c>
       <c r="O94" s="3">
         <v>-8700</v>
       </c>
       <c r="P94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>25900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-50200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-200</v>
       </c>
       <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
+      <c r="AD94" s="3">
+        <v>-200</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8782,8 +9012,11 @@
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8861,8 +9095,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,101 +9479,104 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>28800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>42000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>6900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>127600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3">
         <v>29700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9340,8 +9586,11 @@
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9381,8 +9630,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9444,101 +9693,104 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E102" s="3">
         <v>4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>122700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3">
         <v>24600</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9546,6 +9798,9 @@
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
